--- a/translations.xlsx
+++ b/translations.xlsx
@@ -32,7 +32,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t>English</t>
+    <t>Neko汉化</t>
   </si>
   <si>
     <t>Others</t>
@@ -1254,7 +1254,7 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
